--- a/output/topology_excel/11730.xlsx
+++ b/output/topology_excel/11730.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -517,21 +517,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -567,12 +567,12 @@
         <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
         <v>11</v>
@@ -583,21 +583,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,18 +608,18 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,18 +630,18 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
         <v>11</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -704,156 +704,156 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>387</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>479</v>
+        <v>79</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>512</v>
+        <v>387</v>
       </c>
       <c r="F15" t="n">
-        <v>294</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>599</v>
+        <v>281</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>311</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>205</v>
+        <v>94</v>
       </c>
       <c r="F18" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -861,329 +861,87 @@
         <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>385</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>191</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="F23" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" t="n">
-        <v>11</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>326</v>
-      </c>
-      <c r="F24" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" t="n">
-        <v>14</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>200</v>
-      </c>
-      <c r="F25" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" t="n">
-        <v>15</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>108</v>
-      </c>
-      <c r="F26" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" t="n">
-        <v>6</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>226</v>
-      </c>
-      <c r="F27" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" t="n">
-        <v>7</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>118</v>
-      </c>
-      <c r="F28" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>6</v>
-      </c>
-      <c r="B29" t="n">
-        <v>7</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>180</v>
-      </c>
-      <c r="F29" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>9</v>
-      </c>
-      <c r="B30" t="n">
-        <v>13</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>223</v>
-      </c>
-      <c r="F30" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>10</v>
-      </c>
-      <c r="B31" t="n">
-        <v>11</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>70</v>
-      </c>
-      <c r="F31" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>11</v>
-      </c>
-      <c r="B32" t="n">
-        <v>15</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>315</v>
-      </c>
-      <c r="F32" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>12</v>
-      </c>
-      <c r="B33" t="n">
-        <v>13</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>315</v>
-      </c>
-      <c r="F33" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B34" t="n">
-        <v>15</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="n">
-        <v>182</v>
-      </c>
-      <c r="F34" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/11730.xlsx
+++ b/output/topology_excel/11730.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
